--- a/data/2026/09.2026/Lịch trực OCD on SEP final 15Sep26.xlsx
+++ b/data/2026/09.2026/Lịch trực OCD on SEP final 15Sep26.xlsx
@@ -3199,7 +3199,7 @@
         <v>C9</v>
       </c>
       <c r="AE32" t="str">
-        <v>HC</v>
+        <v/>
       </c>
       <c r="AF32" t="str">
         <v/>
@@ -3211,7 +3211,7 @@
         <v>C9</v>
       </c>
       <c r="AI32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ32">
         <v>2</v>
@@ -3226,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="AN32">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/data/2026/09.2026/Lịch trực OCD on SEP final 15Sep26.xlsx
+++ b/data/2026/09.2026/Lịch trực OCD on SEP final 15Sep26.xlsx
@@ -32,8 +32,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="5">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -3226,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="AN32">
-        <v>154</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
